--- a/branches/proposal/loinc-ontology-valuesets/ValueSet-mii-vs-labor-interpretation-eigenschaften-snomedct.xlsx
+++ b/branches/proposal/loinc-ontology-valuesets/ValueSet-mii-vs-labor-interpretation-eigenschaften-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T02:50:48+00:00</t>
+    <t>2026-10-20T04:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
